--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/集群设备清单表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/集群设备清单表.xlsx
@@ -524,8 +524,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>64</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -558,8 +564,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>174</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -592,8 +604,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -626,8 +644,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>16</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -660,8 +684,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>22</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -694,14 +724,8 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>64</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -734,14 +758,8 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>174</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -774,14 +792,8 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -814,14 +826,8 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>16</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -854,14 +860,8 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>22</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
